--- a/03_initial_joint_configurations/initial_joint_configurations.xlsx
+++ b/03_initial_joint_configurations/initial_joint_configurations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fsbhr-my.sharepoint.com/personal/tknezevic_fsb_hr/Documents/DOKTORAT/01_konferencije_casopisi/predano na review/04_ROMAN_2026/02_nakon reviewa/data/03_initial_joint_configurations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tara Knežević\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="711" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1B18923-D3FF-4FC0-940B-F8D1DB3FF0D8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0CDEC7-95B3-4127-872C-C1445473F0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,7 +216,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -304,11 +304,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -344,6 +355,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -788,7 +801,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="12">
-        <v>2.4434999999999998</v>
+        <v>-2.4434999999999998</v>
       </c>
       <c r="D3" s="13">
         <v>-0.17449999999999999</v>
@@ -810,7 +823,7 @@
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J13" si="6">DEGREES(C3)</f>
-        <v>140.00223724021663</v>
+        <v>-140.00223724021663</v>
       </c>
       <c r="K3" s="13">
         <f t="shared" si="0"/>
@@ -846,7 +859,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="12">
-        <v>-2.4434999999999998</v>
+        <v>2.4434999999999998</v>
       </c>
       <c r="D4" s="13">
         <v>-0.17449999999999999</v>
@@ -868,7 +881,7 @@
       </c>
       <c r="J4" s="12">
         <f t="shared" si="6"/>
-        <v>-140.00223724021663</v>
+        <v>140.00223724021663</v>
       </c>
       <c r="K4" s="13">
         <f t="shared" si="0"/>
@@ -962,7 +975,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="12">
-        <v>2.4434999999999998</v>
+        <v>-2.4434999999999998</v>
       </c>
       <c r="D6" s="13">
         <v>0</v>
@@ -984,7 +997,7 @@
       </c>
       <c r="J6" s="12">
         <f t="shared" si="6"/>
-        <v>140.00223724021663</v>
+        <v>-140.00223724021663</v>
       </c>
       <c r="K6" s="13">
         <f t="shared" si="0"/>
@@ -1020,7 +1033,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="12">
-        <v>-2.4434999999999998</v>
+        <v>2.4434999999999998</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
@@ -1042,7 +1055,7 @@
       </c>
       <c r="J7" s="12">
         <f t="shared" si="6"/>
-        <v>-140.00223724021663</v>
+        <v>140.00223724021663</v>
       </c>
       <c r="K7" s="13">
         <f t="shared" si="0"/>
@@ -1136,7 +1149,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="12">
-        <v>2.4434999999999998</v>
+        <v>-2.4434999999999998</v>
       </c>
       <c r="D9" s="13">
         <v>-0.78539999999999999</v>
@@ -1158,7 +1171,7 @@
       </c>
       <c r="J9" s="12">
         <f t="shared" si="6"/>
-        <v>140.00223724021663</v>
+        <v>-140.00223724021663</v>
       </c>
       <c r="K9" s="13">
         <f t="shared" si="0"/>
@@ -1194,7 +1207,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="12">
-        <v>-2.4434999999999998</v>
+        <v>2.4434999999999998</v>
       </c>
       <c r="D10" s="13">
         <v>-0.78539999999999999</v>
@@ -1216,7 +1229,7 @@
       </c>
       <c r="J10" s="12">
         <f t="shared" si="6"/>
-        <v>-140.00223724021663</v>
+        <v>140.00223724021663</v>
       </c>
       <c r="K10" s="13">
         <f t="shared" si="0"/>
@@ -3763,7 +3776,7 @@
       <c r="B2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="35">
         <v>0</v>
       </c>
       <c r="D2" s="23">
@@ -3821,7 +3834,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="24">
-        <v>1.5708</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
         <v>0.78539999999999999</v>
@@ -3843,7 +3856,7 @@
       </c>
       <c r="J3" s="25">
         <f t="shared" ref="J3:J13" si="1">DEGREES(C3)</f>
-        <v>90.000210459149713</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <f t="shared" si="0"/>
@@ -3878,7 +3891,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="24">
-        <v>1.5708</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <v>0.78539999999999999</v>
@@ -3900,7 +3913,7 @@
       </c>
       <c r="J4" s="25">
         <f t="shared" si="1"/>
-        <v>90.000210459149713</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
@@ -4505,7 +4518,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="14.7" thickBot="1">
       <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
@@ -4562,7 +4575,7 @@
         <v>45.000105229574856</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" ht="14.7" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -4572,17 +4585,17 @@
       <c r="C3" s="25">
         <v>2.6179000000000001</v>
       </c>
-      <c r="D3">
-        <v>-0.26179999999999998</v>
-      </c>
-      <c r="E3">
-        <v>-0.52359999999999995</v>
-      </c>
-      <c r="F3">
-        <v>-1.5708</v>
-      </c>
-      <c r="G3">
-        <v>1.0471999999999999</v>
+      <c r="D3" s="29">
+        <v>-0.78539999999999999</v>
+      </c>
+      <c r="E3" s="29">
+        <v>0</v>
+      </c>
+      <c r="F3" s="29">
+        <v>-2.3561999999999999</v>
+      </c>
+      <c r="G3" s="29">
+        <v>1.5708</v>
       </c>
       <c r="H3">
         <v>0.43630000000000002</v>
@@ -4596,19 +4609,19 @@
       </c>
       <c r="K3">
         <f t="shared" si="0"/>
-        <v>-15.00003507652495</v>
+        <v>-45.000105229574856</v>
       </c>
       <c r="L3">
         <f t="shared" si="0"/>
-        <v>-30.000070153049901</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <f t="shared" si="0"/>
-        <v>-90.000210459149713</v>
+        <v>-135.00031568872456</v>
       </c>
       <c r="N3">
         <f t="shared" si="0"/>
-        <v>60.000140306099802</v>
+        <v>90.000210459149713</v>
       </c>
       <c r="O3">
         <f t="shared" si="0"/>
@@ -4629,17 +4642,17 @@
       <c r="C4" s="25">
         <v>2.6179000000000001</v>
       </c>
-      <c r="D4">
-        <v>-0.26179999999999998</v>
-      </c>
-      <c r="E4">
-        <v>-0.52359999999999995</v>
-      </c>
-      <c r="F4">
-        <v>-1.5708</v>
-      </c>
-      <c r="G4">
-        <v>1.0471999999999999</v>
+      <c r="D4" s="29">
+        <v>-0.78539999999999999</v>
+      </c>
+      <c r="E4" s="29">
+        <v>0</v>
+      </c>
+      <c r="F4" s="29">
+        <v>-2.3561999999999999</v>
+      </c>
+      <c r="G4" s="29">
+        <v>1.5708</v>
       </c>
       <c r="H4">
         <v>2.8797999999999999</v>
@@ -4653,19 +4666,19 @@
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>-15.00003507652495</v>
+        <v>-45.000105229574856</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>-30.000070153049901</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>-90.000210459149713</v>
+        <v>-135.00031568872456</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>60.000140306099802</v>
+        <v>90.000210459149713</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
@@ -5323,8 +5336,8 @@
       <c r="C3" s="25">
         <v>1.5708</v>
       </c>
-      <c r="D3">
-        <v>-1.0471999999999999</v>
+      <c r="D3" s="36">
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5335,8 +5348,8 @@
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>2.0943999999999998</v>
+      <c r="H3" s="36">
+        <v>1.5708</v>
       </c>
       <c r="I3">
         <v>-2.5306999999999999</v>
@@ -5347,7 +5360,7 @@
       </c>
       <c r="K3">
         <f>DEGREES(D3)</f>
-        <v>-60.000140306099802</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <f t="shared" si="0"/>
@@ -5363,7 +5376,7 @@
       </c>
       <c r="O3">
         <f t="shared" si="0"/>
-        <v>120.0002806121996</v>
+        <v>90.000210459149713</v>
       </c>
       <c r="P3" s="31">
         <f>DEGREES(I3)</f>
@@ -5380,8 +5393,8 @@
       <c r="C4" s="25">
         <v>1.5708</v>
       </c>
-      <c r="D4">
-        <v>-1.0471999999999999</v>
+      <c r="D4" s="36">
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5392,8 +5405,8 @@
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>2.0943999999999998</v>
+      <c r="H4" s="36">
+        <v>1.5708</v>
       </c>
       <c r="I4">
         <v>2.5306999999999999</v>
@@ -5404,7 +5417,7 @@
       </c>
       <c r="K4">
         <f t="shared" si="1"/>
-        <v>-60.000140306099802</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <f t="shared" si="1"/>
@@ -5420,7 +5433,7 @@
       </c>
       <c r="O4">
         <f t="shared" si="1"/>
-        <v>120.0002806121996</v>
+        <v>90.000210459149713</v>
       </c>
       <c r="P4" s="31">
         <f t="shared" si="1"/>
@@ -5517,7 +5530,7 @@
         <v>90.000210459149713</v>
       </c>
       <c r="K6">
-        <f>DEGREES(D6)</f>
+        <f t="shared" ref="K6:K11" si="5">DEGREES(D6)</f>
         <v>0</v>
       </c>
       <c r="L6">
@@ -5574,7 +5587,7 @@
         <v>90.000210459149713</v>
       </c>
       <c r="K7">
-        <f>DEGREES(D7)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L7">
@@ -5631,7 +5644,7 @@
         <v>90.000210459149713</v>
       </c>
       <c r="K8">
-        <f>DEGREES(D8)</f>
+        <f t="shared" si="5"/>
         <v>-60.000140306099802</v>
       </c>
       <c r="L8">
@@ -5688,7 +5701,7 @@
         <v>90.000210459149713</v>
       </c>
       <c r="K9">
-        <f>DEGREES(D9)</f>
+        <f t="shared" si="5"/>
         <v>-60.000140306099802</v>
       </c>
       <c r="L9">
@@ -5745,7 +5758,7 @@
         <v>90.000210459149713</v>
       </c>
       <c r="K10">
-        <f>DEGREES(D10)</f>
+        <f t="shared" si="5"/>
         <v>-60.000140306099802</v>
       </c>
       <c r="L10">
@@ -5802,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <f>DEGREES(D11)</f>
+        <f t="shared" si="5"/>
         <v>-44.999999977227887</v>
       </c>
       <c r="L11">
@@ -5852,31 +5865,31 @@
         <v>2.4434999999999998</v>
       </c>
       <c r="I12">
-        <f t="shared" ref="I12:I13" si="5">RADIANS(W12)</f>
+        <f t="shared" ref="I12:I13" si="6">RADIANS(W12)</f>
         <v>0</v>
       </c>
       <c r="J12" s="25">
-        <f t="shared" ref="J12:O13" si="6">DEGREES(C12)</f>
+        <f t="shared" ref="J12:O13" si="7">DEGREES(C12)</f>
         <v>-140.00223724021663</v>
       </c>
       <c r="K12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>30.000070153049901</v>
       </c>
       <c r="L12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>120.0002806121996</v>
       </c>
       <c r="M12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-150.00035076524952</v>
       </c>
       <c r="N12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-60.000140306099802</v>
       </c>
       <c r="O12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>140.00223724021663</v>
       </c>
       <c r="P12" s="31">
@@ -5910,31 +5923,31 @@
         <v>1.5708</v>
       </c>
       <c r="I13" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J13" s="26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K13" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-80.00209693411685</v>
       </c>
       <c r="L13" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-130.00412371518379</v>
       </c>
       <c r="M13" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-20.001956628017041</v>
       </c>
       <c r="N13" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>150.00035076524952</v>
       </c>
       <c r="O13" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>90.000210459149713</v>
       </c>
       <c r="P13" s="32">
